--- a/test_scenarios/vat_repayment/Demo_Company__UK__-_Trial_Balance.xlsx
+++ b/test_scenarios/vat_repayment/Demo_Company__UK__-_Trial_Balance.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trial Balance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Trial Balance" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -1158,9 +1158,11 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>244.34</v>
-      </c>
-      <c r="E29" s="11" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>1000</v>
+      </c>
       <c r="F29" s="12" t="n">
         <v>1643.62</v>
       </c>
